--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/02_FR2 - Eskalasyon ve Müşteri Koruma/EKG-KLT-FRM-12_kalite_alarmi_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/02_FR2 - Eskalasyon ve Müşteri Koruma/EKG-KLT-FRM-12_kalite_alarmi_formu.xlsx
@@ -810,7 +810,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-12&amp;C&amp;"Arial,Regular"&amp;11Kalite Alarmı Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc18b75a8daf9494a"/>
   <x:tableParts count="1">
@@ -1059,7 +1060,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-12&amp;C&amp;"Arial,Regular"&amp;11Kalite Alarmı Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R632d6c0eddba497a"/>
   <x:tableParts count="1">
@@ -1328,7 +1330,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-12&amp;C&amp;"Arial,Regular"&amp;11Kalite Alarmı Formu</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7b75aa0ce244249"/>
   <x:tableParts count="1">
